--- a/doc/6-3#装配线/6-3地址表代码A线与B线.xlsx
+++ b/doc/6-3#装配线/6-3地址表代码A线与B线.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="119">
   <si>
     <t>地址</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>m2500</t>
+  </si>
+  <si>
+    <t>m724</t>
   </si>
 </sst>
 </file>
@@ -1785,8 +1788,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="14.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -1968,7 +1971,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>107</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -1990,7 +1993,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>111</v>
       </c>
@@ -2001,7 +2004,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -2012,7 +2015,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -2023,7 +2026,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>117</v>
       </c>
@@ -2033,8 +2036,11 @@
       <c r="C22" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="E22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>117</v>
       </c>
